--- a/outputs/M4_real_interest_robustness_regression_detail.xlsx
+++ b/outputs/M4_real_interest_robustness_regression_detail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>variable</t>
   </si>
@@ -40,19 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp</t>
+  </si>
+  <si>
+    <t>ln_gdppc</t>
+  </si>
+  <si>
+    <t>xr_dep_pct</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp</t>
   </si>
   <si>
     <t>real_interest_rate_pct</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp</t>
-  </si>
-  <si>
-    <t>ln_gdppc</t>
-  </si>
-  <si>
-    <t>xr_dep_pct</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,22 +444,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>30.95041051989586</v>
+        <v>22.21753087747955</v>
       </c>
       <c r="C2">
-        <v>30.15857415284886</v>
+        <v>17.29842738264423</v>
       </c>
       <c r="D2">
-        <v>1.026255762723855</v>
+        <v>1.284367092223119</v>
       </c>
       <c r="E2">
-        <v>0.3082548030769807</v>
+        <v>0.2032479907684324</v>
       </c>
       <c r="F2">
-        <v>-29.18407839585763</v>
+        <v>-12.283094669745</v>
       </c>
       <c r="G2">
-        <v>91.08489943564935</v>
+        <v>56.7181564247041</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -464,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.09861997664650304</v>
+        <v>-0.5940035411358737</v>
       </c>
       <c r="C3">
-        <v>0.06618283299687676</v>
+        <v>0.1500142102104957</v>
       </c>
       <c r="D3">
-        <v>1.490114160739493</v>
+        <v>-3.959648491315488</v>
       </c>
       <c r="E3">
-        <v>0.1406234667970452</v>
+        <v>0.000178133615196252</v>
       </c>
       <c r="F3">
-        <v>-0.03334484427285397</v>
+        <v>-0.8931974492727304</v>
       </c>
       <c r="G3">
-        <v>0.2305847975658601</v>
+        <v>-0.2948096329990171</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -487,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.09108843780967558</v>
+        <v>-0.03745371967266513</v>
       </c>
       <c r="C4">
-        <v>0.09766243282876634</v>
+        <v>0.01251937302493992</v>
       </c>
       <c r="D4">
-        <v>-0.9326865527646943</v>
+        <v>-2.991660972003419</v>
       </c>
       <c r="E4">
-        <v>0.3541427816427452</v>
+        <v>0.003829261109752347</v>
       </c>
       <c r="F4">
-        <v>-0.2858217980362631</v>
+        <v>-0.06242282184971239</v>
       </c>
       <c r="G4">
-        <v>0.1036449224169119</v>
+        <v>-0.01248461749561786</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -510,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-0.03794205872246072</v>
+        <v>-1.277697563821016</v>
       </c>
       <c r="C5">
-        <v>0.02610769732118235</v>
+        <v>2.100754087025277</v>
       </c>
       <c r="D5">
-        <v>-1.453290125731488</v>
+        <v>-0.6082090101418151</v>
       </c>
       <c r="E5">
-        <v>0.1505490527246922</v>
+        <v>0.5450173091852943</v>
       </c>
       <c r="F5">
-        <v>-0.08999932864575327</v>
+        <v>-5.467519477689223</v>
       </c>
       <c r="G5">
-        <v>0.01411521120083183</v>
+        <v>2.912124350047191</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -533,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-3.425709214376441</v>
+        <v>0.1472813119985956</v>
       </c>
       <c r="C6">
-        <v>3.727705058006158</v>
+        <v>0.06472851490703524</v>
       </c>
       <c r="D6">
-        <v>-0.9189861217745467</v>
+        <v>2.275369861491876</v>
       </c>
       <c r="E6">
-        <v>0.3612144311420078</v>
+        <v>0.02594836173507531</v>
       </c>
       <c r="F6">
-        <v>-10.85854199207241</v>
+        <v>0.01818435967817011</v>
       </c>
       <c r="G6">
-        <v>4.00712356331953</v>
+        <v>0.2763782643190212</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -556,22 +559,45 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.01465189220196079</v>
+        <v>0.03344479078447644</v>
       </c>
       <c r="C7">
-        <v>0.07262874009194842</v>
+        <v>0.05025166591893871</v>
       </c>
       <c r="D7">
-        <v>0.2017368356302396</v>
+        <v>0.6655459112226537</v>
       </c>
       <c r="E7">
-        <v>0.84069935404453</v>
+        <v>0.5078885552638224</v>
       </c>
       <c r="F7">
-        <v>-0.1301657024193634</v>
+        <v>-0.06677899665258225</v>
       </c>
       <c r="G7">
-        <v>0.159469486823285</v>
+        <v>0.1336685782215351</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>-0.6600910154879333</v>
+      </c>
+      <c r="C8">
+        <v>0.2290450074697396</v>
+      </c>
+      <c r="D8">
+        <v>-2.881927105855567</v>
+      </c>
+      <c r="E8">
+        <v>0.005244179360424761</v>
+      </c>
+      <c r="F8">
+        <v>-1.11690687865149</v>
+      </c>
+      <c r="G8">
+        <v>-0.203275152324376</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M4_real_interest_robustness_regression_detail.xlsx
+++ b/outputs/M4_real_interest_robustness_regression_detail.xlsx
@@ -40,6 +40,12 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>broad_money_growth_pct</t>
+  </si>
+  <si>
+    <t>real_interest_rate_pct</t>
+  </si>
+  <si>
     <t>inflation_gdp_deflator_pct</t>
   </si>
   <si>
@@ -50,12 +56,6 @@
   </si>
   <si>
     <t>xr_dep_pct</t>
-  </si>
-  <si>
-    <t>broad_money_pct_gdp</t>
-  </si>
-  <si>
-    <t>real_interest_rate_pct</t>
   </si>
 </sst>
 </file>
@@ -444,22 +444,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>22.21753087747955</v>
+        <v>32.68905537262353</v>
       </c>
       <c r="C2">
-        <v>17.29842738264423</v>
+        <v>34.00950519731523</v>
       </c>
       <c r="D2">
-        <v>1.284367092223119</v>
+        <v>0.9611740947999462</v>
       </c>
       <c r="E2">
-        <v>0.2032479907684324</v>
+        <v>0.3382768336821262</v>
       </c>
       <c r="F2">
-        <v>-12.283094669745</v>
+        <v>-34.60456117798218</v>
       </c>
       <c r="G2">
-        <v>56.7181564247041</v>
+        <v>99.98267192322923</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>-0.5940035411358737</v>
+        <v>0.03508341270296937</v>
       </c>
       <c r="C3">
-        <v>0.1500142102104957</v>
+        <v>0.0425516789701304</v>
       </c>
       <c r="D3">
-        <v>-3.959648491315488</v>
+        <v>0.8244895043412164</v>
       </c>
       <c r="E3">
-        <v>0.000178133615196252</v>
+        <v>0.4111952509197363</v>
       </c>
       <c r="F3">
-        <v>-0.8931974492727304</v>
+        <v>-0.04911235408597156</v>
       </c>
       <c r="G3">
-        <v>-0.2948096329990171</v>
+        <v>0.1192791794919103</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.03745371967266513</v>
+        <v>-0.3224511910681314</v>
       </c>
       <c r="C4">
-        <v>0.01251937302493992</v>
+        <v>0.2370203103772127</v>
       </c>
       <c r="D4">
-        <v>-2.991660972003419</v>
+        <v>-1.360436962363931</v>
       </c>
       <c r="E4">
-        <v>0.003829261109752347</v>
+        <v>0.1760826008894778</v>
       </c>
       <c r="F4">
-        <v>-0.06242282184971239</v>
+        <v>-0.7914363700259487</v>
       </c>
       <c r="G4">
-        <v>-0.01248461749561786</v>
+        <v>0.146533987889686</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-1.277697563821016</v>
+        <v>-0.2957207396969821</v>
       </c>
       <c r="C5">
-        <v>2.100754087025277</v>
+        <v>0.1987534776558138</v>
       </c>
       <c r="D5">
-        <v>-0.6082090101418151</v>
+        <v>-1.48787705847889</v>
       </c>
       <c r="E5">
-        <v>0.5450173091852943</v>
+        <v>0.139242758079978</v>
       </c>
       <c r="F5">
-        <v>-5.467519477689223</v>
+        <v>-0.6889884522341685</v>
       </c>
       <c r="G5">
-        <v>2.912124350047191</v>
+        <v>0.09754697284020436</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.1472813119985956</v>
+        <v>-0.01264718653293245</v>
       </c>
       <c r="C6">
-        <v>0.06472851490703524</v>
+        <v>0.01837076495214232</v>
       </c>
       <c r="D6">
-        <v>2.275369861491876</v>
+        <v>-0.688440931331909</v>
       </c>
       <c r="E6">
-        <v>0.02594836173507531</v>
+        <v>0.4924210015598169</v>
       </c>
       <c r="F6">
-        <v>0.01818435967817011</v>
+        <v>-0.04899688363256455</v>
       </c>
       <c r="G6">
-        <v>0.2763782643190212</v>
+        <v>0.02370251056669964</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.03344479078447644</v>
+        <v>-0.9521378614649724</v>
       </c>
       <c r="C7">
-        <v>0.05025166591893871</v>
+        <v>1.282569512020566</v>
       </c>
       <c r="D7">
-        <v>0.6655459112226537</v>
+        <v>-0.7423674526341814</v>
       </c>
       <c r="E7">
-        <v>0.5078885552638224</v>
+        <v>0.4592248751982728</v>
       </c>
       <c r="F7">
-        <v>-0.06677899665258225</v>
+        <v>-3.489920767763262</v>
       </c>
       <c r="G7">
-        <v>0.1336685782215351</v>
+        <v>1.585645044833317</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +582,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.6600910154879333</v>
+        <v>0.08007409570939061</v>
       </c>
       <c r="C8">
-        <v>0.2290450074697396</v>
+        <v>0.04273981930602314</v>
       </c>
       <c r="D8">
-        <v>-2.881927105855567</v>
+        <v>1.873524432474756</v>
       </c>
       <c r="E8">
-        <v>0.005244179360424761</v>
+        <v>0.06327633049264358</v>
       </c>
       <c r="F8">
-        <v>-1.11690687865149</v>
+        <v>-0.004493938877855957</v>
       </c>
       <c r="G8">
-        <v>-0.203275152324376</v>
+        <v>0.1646421302966372</v>
       </c>
     </row>
   </sheetData>
